--- a/Result/profitability/5371.xlsx
+++ b/Result/profitability/5371.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.84</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3125</v>
+        <v>0.2225</v>
       </c>
       <c r="N2" t="n">
-        <v>16.37625</v>
+        <v>16.21125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.29</v>
       </c>
       <c r="M3" t="n">
-        <v>0.40875</v>
+        <v>0.3225</v>
       </c>
       <c r="N3" t="n">
-        <v>15.79875</v>
+        <v>15.3325</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.39</v>
       </c>
       <c r="M4" t="n">
-        <v>0.52125</v>
+        <v>0.49</v>
       </c>
       <c r="N4" t="n">
-        <v>15.17375</v>
+        <v>14.89375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.24</v>
       </c>
       <c r="M5" t="n">
-        <v>0.485</v>
+        <v>0.4412499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>14.32875</v>
+        <v>13.97125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.36</v>
       </c>
       <c r="M6" t="n">
-        <v>0.51125</v>
+        <v>0.45625</v>
       </c>
       <c r="N6" t="n">
-        <v>14.10125</v>
+        <v>14.115</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.76</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5762499999999999</v>
+        <v>0.4874999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>13.8125</v>
+        <v>13.46</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.17</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6587499999999999</v>
+        <v>0.6712499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>13.1525</v>
+        <v>13.11125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>1.42</v>
       </c>
       <c r="M9" t="n">
-        <v>0.87375</v>
+        <v>0.8737499999999999</v>
       </c>
       <c r="N9" t="n">
         <v>12.97</v>
@@ -1645,7 +1645,7 @@
         <v>1.33</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9349999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>13.41375</v>
@@ -1772,7 +1772,7 @@
         <v>1.68</v>
       </c>
       <c r="M11" t="n">
-        <v>0.98375</v>
+        <v>0.9837499999999999</v>
       </c>
       <c r="N11" t="n">
         <v>13.71625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5371</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>10035</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8501</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1534</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-83</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.83%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>168</v>
+      </c>
+      <c r="J75" t="n">
+        <v>85</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-77</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1825</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.93875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.3300000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02112676056338025</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.859999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1575757575757576</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
